--- a/Team-Data/2013-14/3-5-2013-14.xlsx
+++ b/Team-Data/2013-14/3-5-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,46 +728,46 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.441</v>
+        <v>0.448</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="J2" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.458</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M2" t="n">
         <v>25.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.377</v>
+        <v>0.381</v>
       </c>
       <c r="O2" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P2" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R2" t="n">
         <v>9</v>
@@ -709,22 +776,22 @@
         <v>31.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U2" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="V2" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W2" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z2" t="n">
         <v>18.9</v>
@@ -733,13 +800,13 @@
         <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.5</v>
+        <v>101.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -751,25 +818,25 @@
         <v>18</v>
       </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
         <v>20</v>
@@ -793,16 +860,16 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
         <v>23</v>
       </c>
       <c r="AY2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -811,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>0.328</v>
+        <v>0.333</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J3" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L3" t="n">
         <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.326</v>
+        <v>0.327</v>
       </c>
       <c r="O3" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P3" t="n">
         <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
         <v>11.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T3" t="n">
         <v>43</v>
       </c>
       <c r="U3" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W3" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X3" t="n">
         <v>4.5</v>
@@ -909,25 +976,25 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA3" t="n">
         <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.3</v>
+        <v>95.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.9</v>
+        <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
@@ -936,7 +1003,7 @@
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
         <v>11</v>
@@ -954,10 +1021,10 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>11</v>
@@ -966,7 +1033,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -975,13 +1042,13 @@
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
@@ -993,7 +1060,7 @@
         <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
         <v>24</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -1025,64 +1092,64 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
       </c>
       <c r="I4" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J4" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L4" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.364</v>
+        <v>0.359</v>
       </c>
       <c r="O4" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S4" t="n">
         <v>29.7</v>
       </c>
       <c r="T4" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W4" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X4" t="n">
         <v>4</v>
@@ -1091,31 +1158,31 @@
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF4" t="n">
         <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1133,19 +1200,19 @@
         <v>12</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
         <v>28</v>
@@ -1157,10 +1224,10 @@
         <v>23</v>
       </c>
       <c r="AV4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW4" t="n">
         <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>8</v>
       </c>
       <c r="AX4" t="n">
         <v>26</v>
@@ -1169,13 +1236,13 @@
         <v>8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
         <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.459</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="J5" t="n">
         <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.728</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S5" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U5" t="n">
         <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="W5" t="n">
         <v>6.2</v>
@@ -1279,19 +1346,19 @@
         <v>21.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.5</v>
+        <v>95.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.8</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
@@ -1303,19 +1370,19 @@
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM5" t="n">
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1327,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
         <v>8</v>
@@ -1348,16 +1415,16 @@
         <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
         <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
         <v>80.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.431</v>
+        <v>0.429</v>
       </c>
       <c r="L6" t="n">
         <v>6</v>
@@ -1419,19 +1486,19 @@
         <v>17.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.342</v>
+        <v>0.344</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
         <v>33.1</v>
@@ -1440,13 +1507,13 @@
         <v>45.1</v>
       </c>
       <c r="U6" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V6" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
         <v>5.2</v>
@@ -1458,19 +1525,19 @@
         <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.3</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1509,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1536,7 +1603,7 @@
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>20</v>
@@ -1664,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ7" t="n">
         <v>6</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1691,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS7" t="n">
         <v>15</v>
@@ -1703,10 +1770,10 @@
         <v>24</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1820,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
         <v>36</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.581</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J8" t="n">
         <v>83.59999999999999</v>
@@ -1783,25 +1850,25 @@
         <v>22.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O8" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P8" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.801</v>
+        <v>0.8</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S8" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T8" t="n">
-        <v>40.2</v>
+        <v>40.4</v>
       </c>
       <c r="U8" t="n">
         <v>23.7</v>
@@ -1810,7 +1877,7 @@
         <v>13.4</v>
       </c>
       <c r="W8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X8" t="n">
         <v>4.2</v>
@@ -1819,40 +1886,40 @@
         <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA8" t="n">
         <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
         <v>12</v>
       </c>
       <c r="AK8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
         <v>8</v>
@@ -1861,13 +1928,13 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1897,10 +1964,10 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB8" t="n">
         <v>8</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>0.433</v>
+        <v>0.424</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,10 +2020,10 @@
         <v>37.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K9" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L9" t="n">
         <v>8.300000000000001</v>
@@ -1965,34 +2032,34 @@
         <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P9" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.719</v>
+        <v>0.716</v>
       </c>
       <c r="R9" t="n">
         <v>12.5</v>
       </c>
       <c r="S9" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T9" t="n">
         <v>45.4</v>
       </c>
       <c r="U9" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V9" t="n">
         <v>15.6</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
         <v>5.7</v>
@@ -2001,22 +2068,22 @@
         <v>5.5</v>
       </c>
       <c r="Z9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="AD9" t="n">
         <v>23</v>
       </c>
-      <c r="AA9" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>102.8</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>21</v>
-      </c>
       <c r="AE9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
         <v>19</v>
@@ -2028,10 +2095,10 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK9" t="n">
         <v>19</v>
@@ -2043,10 +2110,10 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>5</v>
@@ -2061,7 +2128,7 @@
         <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="n">
         <v>15</v>
@@ -2070,10 +2137,10 @@
         <v>26</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>23</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -2117,19 +2184,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H10" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I10" t="n">
         <v>39</v>
@@ -2141,40 +2208,40 @@
         <v>0.449</v>
       </c>
       <c r="L10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M10" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.311</v>
+        <v>0.312</v>
       </c>
       <c r="O10" t="n">
         <v>17.1</v>
       </c>
       <c r="P10" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.669</v>
+        <v>0.668</v>
       </c>
       <c r="R10" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="S10" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T10" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="U10" t="n">
         <v>20.9</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X10" t="n">
         <v>5.2</v>
@@ -2183,19 +2250,19 @@
         <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA10" t="n">
         <v>20.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.7</v>
+        <v>-2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE10" t="n">
         <v>20</v>
@@ -2207,7 +2274,7 @@
         <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>6</v>
@@ -2219,7 +2286,7 @@
         <v>17</v>
       </c>
       <c r="AL10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM10" t="n">
         <v>26</v>
@@ -2255,10 +2322,10 @@
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -2299,46 +2366,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.613</v>
+        <v>0.607</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="J11" t="n">
-        <v>85.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K11" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L11" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="O11" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R11" t="n">
         <v>11.3</v>
@@ -2350,13 +2417,13 @@
         <v>45.7</v>
       </c>
       <c r="U11" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V11" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X11" t="n">
         <v>5.2</v>
@@ -2371,13 +2438,13 @@
         <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,16 +2456,16 @@
         <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL11" t="n">
         <v>5</v>
@@ -2407,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
         <v>23</v>
@@ -2437,7 +2504,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2452,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2502,40 +2569,40 @@
         <v>79.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L12" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P12" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.695</v>
+        <v>0.696</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
         <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U12" t="n">
         <v>20.9</v>
       </c>
       <c r="V12" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="W12" t="n">
         <v>7.3</v>
@@ -2547,22 +2614,22 @@
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA12" t="n">
         <v>24.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2574,7 +2641,7 @@
         <v>14</v>
       </c>
       <c r="AI12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2589,10 +2656,10 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2604,10 +2671,10 @@
         <v>16</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
         <v>21</v>
@@ -2619,13 +2686,13 @@
         <v>19</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
         <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="n">
-        <v>0.754</v>
+        <v>0.767</v>
       </c>
       <c r="H13" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J13" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
         <v>6.8</v>
@@ -2693,7 +2760,7 @@
         <v>19.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
         <v>18.5</v>
@@ -2708,10 +2775,10 @@
         <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="T13" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U13" t="n">
         <v>20.4</v>
@@ -2720,10 +2787,10 @@
         <v>15.1</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y13" t="n">
         <v>4.6</v>
@@ -2735,13 +2802,13 @@
         <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,19 +2820,19 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>13</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM13" t="n">
         <v>23</v>
@@ -2774,10 +2841,10 @@
         <v>22</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2795,22 +2862,22 @@
         <v>25</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
         <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
         <v>20</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2944,7 +3011,7 @@
         <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2956,7 +3023,7 @@
         <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -2980,7 +3047,7 @@
         <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>18</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -3105,22 +3172,22 @@
         <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF15" t="n">
         <v>25</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>24</v>
       </c>
       <c r="AG15" t="n">
         <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ15" t="n">
         <v>10</v>
@@ -3168,7 +3235,7 @@
         <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -3209,64 +3276,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
         <v>34</v>
       </c>
       <c r="F16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.46</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
         <v>14.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O16" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R16" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S16" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T16" t="n">
         <v>42.1</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W16" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X16" t="n">
         <v>4.7</v>
@@ -3278,22 +3345,22 @@
         <v>19.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AB16" t="n">
         <v>95.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3302,13 +3369,13 @@
         <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3326,7 +3393,7 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR16" t="n">
         <v>14</v>
@@ -3350,13 +3417,13 @@
         <v>17</v>
       </c>
       <c r="AY16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
       </c>
       <c r="BA16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>6.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>3</v>
@@ -3496,7 +3563,7 @@
         <v>12</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2</v>
+        <v>0.203</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3600,58 +3667,58 @@
         <v>7.4</v>
       </c>
       <c r="M18" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N18" t="n">
         <v>0.361</v>
       </c>
       <c r="O18" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R18" t="n">
         <v>11.7</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U18" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y18" t="n">
         <v>5.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA18" t="n">
         <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3681,10 +3748,10 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
         <v>27</v>
@@ -3702,16 +3769,16 @@
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" t="n">
         <v>30</v>
       </c>
       <c r="F19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.508</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>38.5</v>
       </c>
       <c r="J19" t="n">
-        <v>87.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0.439</v>
@@ -3785,25 +3852,25 @@
         <v>21.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O19" t="n">
         <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R19" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="S19" t="n">
         <v>32.8</v>
       </c>
       <c r="T19" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="U19" t="n">
         <v>23.3</v>
@@ -3821,7 +3888,7 @@
         <v>5.8</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AA19" t="n">
         <v>23.6</v>
@@ -3830,19 +3897,19 @@
         <v>106.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
       </c>
       <c r="AF19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
@@ -3851,7 +3918,7 @@
         <v>11</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3860,7 +3927,7 @@
         <v>17</v>
       </c>
       <c r="AM19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN19" t="n">
         <v>27</v>
@@ -3872,7 +3939,7 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
@@ -3884,10 +3951,10 @@
         <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>-2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>13</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
         <v>15</v>
@@ -4066,7 +4133,7 @@
         <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
         <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>0.355</v>
+        <v>0.344</v>
       </c>
       <c r="H21" t="n">
         <v>48.6</v>
       </c>
       <c r="I21" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="J21" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K21" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L21" t="n">
         <v>9</v>
@@ -4149,16 +4216,16 @@
         <v>24.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O21" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="P21" t="n">
         <v>19.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
@@ -4182,37 +4249,37 @@
         <v>4.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA21" t="n">
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.7</v>
+        <v>97.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ21" t="n">
         <v>13</v>
@@ -4236,7 +4303,7 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR21" t="n">
         <v>18</v>
@@ -4257,7 +4324,7 @@
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4266,10 +4333,10 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC21" t="n">
         <v>23</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -4379,25 +4446,25 @@
         <v>6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4409,13 +4476,13 @@
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4436,7 +4503,7 @@
         <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4445,10 +4512,10 @@
         <v>3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -4483,22 +4550,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E23" t="n">
         <v>19</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G23" t="n">
-        <v>0.302</v>
+        <v>0.306</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J23" t="n">
         <v>83</v>
@@ -4507,19 +4574,19 @@
         <v>0.442</v>
       </c>
       <c r="L23" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P23" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q23" t="n">
         <v>0.765</v>
@@ -4528,37 +4595,37 @@
         <v>9.5</v>
       </c>
       <c r="S23" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
         <v>20.8</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W23" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4573,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -4630,7 +4697,7 @@
         <v>8</v>
       </c>
       <c r="BA23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
         <v>24</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI24" t="n">
         <v>12</v>
@@ -4767,7 +4834,7 @@
         <v>27</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM24" t="n">
         <v>13</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4934,7 +5001,7 @@
         <v>9</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>19</v>
@@ -4946,7 +5013,7 @@
         <v>9</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>4</v>
@@ -4958,7 +5025,7 @@
         <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
@@ -4979,10 +5046,10 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
         <v>14</v>
@@ -4994,7 +5061,7 @@
         <v>25</v>
       </c>
       <c r="BA25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F26" t="n">
         <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J26" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="K26" t="n">
         <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O26" t="n">
         <v>19.1</v>
@@ -5068,16 +5135,16 @@
         <v>23.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.824</v>
+        <v>0.823</v>
       </c>
       <c r="R26" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="S26" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="T26" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="U26" t="n">
         <v>23.5</v>
@@ -5101,16 +5168,16 @@
         <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.7</v>
+        <v>107.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26" t="n">
         <v>5</v>
@@ -5122,22 +5189,22 @@
         <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK26" t="n">
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS26" t="n">
         <v>5</v>
@@ -5161,7 +5228,7 @@
         <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5176,7 +5243,7 @@
         <v>6</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB26" t="n">
         <v>1</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -5211,70 +5278,70 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F27" t="n">
         <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0.361</v>
+        <v>0.35</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J27" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O27" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P27" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R27" t="n">
         <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U27" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V27" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z27" t="n">
         <v>23</v>
@@ -5283,13 +5350,13 @@
         <v>23</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.7</v>
+        <v>101.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.1</v>
+        <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
@@ -5328,10 +5395,10 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS27" t="n">
         <v>16</v>
@@ -5343,7 +5410,7 @@
         <v>29</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
         <v>18</v>
@@ -5361,7 +5428,7 @@
         <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -5653,13 +5720,13 @@
         <v>3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG29" t="n">
         <v>12</v>
@@ -5668,7 +5735,7 @@
         <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ29" t="n">
         <v>17</v>
@@ -5683,13 +5750,13 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
@@ -5698,7 +5765,7 @@
         <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
         <v>14</v>
@@ -5722,7 +5789,7 @@
         <v>27</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G30" t="n">
-        <v>0.344</v>
+        <v>0.35</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
@@ -5796,16 +5863,16 @@
         <v>21.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.747</v>
+        <v>0.75</v>
       </c>
       <c r="R30" t="n">
         <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T30" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U30" t="n">
         <v>20</v>
@@ -5823,28 +5890,28 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA30" t="n">
         <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH30" t="n">
         <v>25</v>
@@ -5865,7 +5932,7 @@
         <v>24</v>
       </c>
       <c r="AN30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO30" t="n">
         <v>24</v>
@@ -5877,7 +5944,7 @@
         <v>22</v>
       </c>
       <c r="AR30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5895,10 +5962,10 @@
         <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
@@ -5957,28 +6024,28 @@
         <v>38.6</v>
       </c>
       <c r="J31" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.456</v>
+        <v>0.454</v>
       </c>
       <c r="L31" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.384</v>
+        <v>0.383</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.731</v>
+        <v>0.729</v>
       </c>
       <c r="R31" t="n">
         <v>10.9</v>
@@ -5987,19 +6054,19 @@
         <v>31.5</v>
       </c>
       <c r="T31" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U31" t="n">
         <v>23.3</v>
       </c>
       <c r="V31" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W31" t="n">
         <v>8.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
         <v>4</v>
@@ -6008,16 +6075,16 @@
         <v>20.7</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.7</v>
+        <v>100.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6038,7 +6105,7 @@
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6050,7 +6117,7 @@
         <v>3</v>
       </c>
       <c r="AO31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
         <v>24</v>
@@ -6059,7 +6126,7 @@
         <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS31" t="n">
         <v>18</v>
@@ -6068,16 +6135,16 @@
         <v>17</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV31" t="n">
         <v>14</v>
       </c>
       <c r="AW31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-5-2013-14</t>
+          <t>2014-03-05</t>
         </is>
       </c>
     </row>
